--- a/output/pdf_financials_xlsx/PMET.xlsx
+++ b/output/pdf_financials_xlsx/PMET.xlsx
@@ -6166,49 +6166,49 @@
         <v>0.18837</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.12017</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.200395</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.330153</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.414132</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.490583</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.622041</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.847553</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.544859</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.206537</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.607953</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.922</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>15.723</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>22.675</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>31.457</v>
       </c>
     </row>
     <row r="93">
@@ -7724,10 +7724,10 @@
         <v>-0.5224220000000001</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>-0.453433</v>
+        <v>-7.623522</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-3.866496</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -7739,16 +7739,16 @@
         <v>0</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-27.084</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-53.291</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-74.77200000000001</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-51.838</v>
       </c>
     </row>
     <row r="119">
@@ -10938,7 +10938,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -12244,7 +12248,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -15982,7 +15990,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -17316,7 +17328,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -19442,7 +19458,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -21746,7 +21766,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -21958,7 +21982,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -22486,7 +22514,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -23964,7 +23996,11 @@
           <t>RESERVES</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -26256,7 +26292,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -28528,7 +28568,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -35662,7 +35706,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PMET.xlsx
+++ b/output/pdf_financials_xlsx/PMET.xlsx
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000592</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1089,34 +1089,34 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>5e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001708</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00014</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>4.731</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>3.423</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="13">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.052639</v>
+        <v>-0.053231</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.142963</v>
@@ -2078,34 +2078,34 @@
         <v>-0.461306</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.964246</v>
+        <v>-0.964296</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.96469</v>
+        <v>-0.966398</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-8.578841000000001</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.528956</v>
+        <v>-0.529096</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.775048</v>
+        <v>-0.775077</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.882</v>
+        <v>-3.884</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.964</v>
+        <v>-6.986</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>12.614</v>
+        <v>7.883</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>5.22</v>
+        <v>1.797</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-7.751</v>
+        <v>-10.299</v>
       </c>
     </row>
     <row r="28">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.052639</v>
+        <v>-0.053231</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.142963</v>
@@ -2200,34 +2200,34 @@
         <v>-0.461306</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.964246</v>
+        <v>-0.964296</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.96469</v>
+        <v>-0.966398</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-8.578841000000001</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.528956</v>
+        <v>-0.529096</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.775048</v>
+        <v>-0.775077</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.882</v>
+        <v>-3.884</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.943</v>
+        <v>-6.965</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>12.614</v>
+        <v>7.883</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>5.22</v>
+        <v>1.797</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-7.751</v>
+        <v>-10.299</v>
       </c>
     </row>
     <row r="30">
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.00273</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.355522</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.296414</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
         <v>0.963627</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1.122915</v>
+        <v>13.513182</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.849114</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.255889</v>
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.00273</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.355522</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.296414</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -2648,10 +2648,10 @@
         <v>0.963627</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.361803</v>
+        <v>13.75207</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.849114</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.255889</v>
@@ -3353,13 +3353,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.00273</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.355522</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.300914</v>
+        <v>0.0045</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.0025</v>
@@ -3380,10 +3380,10 @@
         <v>0.053613</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>13.180483</v>
+        <v>0.790216</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>7.103638</v>
+        <v>0.254524</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.018179</v>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -18286,7 +18286,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -21044,7 +21048,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -22940,7 +22944,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -49316,7 +49320,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -51112,7 +51116,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -55976,7 +55980,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -66414,7 +66418,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E550" s="5" t="n">

--- a/output/pdf_financials_xlsx/PMET.xlsx
+++ b/output/pdf_financials_xlsx/PMET.xlsx
@@ -1373,7 +1373,7 @@
         <v>0.053231</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.142963</v>
+        <v>-0.004418</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0.048169</v>
@@ -2337,7 +2337,7 @@
         <v>-101.124641425559</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-100</v>
+        <v>-3.090310080230549</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-9.372312481758927</v>
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.046405</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -25486,7 +25486,11 @@
           <t>Deferred income tax expense 17</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -31086,7 +31090,11 @@
           <t>Deferred income tax expense 16</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -35172,7 +35180,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -45210,7 +45222,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E348" s="5" t="n">
         <v>0.0786</v>
       </c>
@@ -46478,7 +46494,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E360" s="5" t="n">
         <v>-0.025228</v>
       </c>
@@ -65358,7 +65378,11 @@
           <t>FUTURE INCOME TAX RECOVERY (Note 8)</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E540" s="5" t="n">
         <v>0.025228</v>
       </c>
